--- a/RUC/RUC_Contenido_t.xlsx
+++ b/RUC/RUC_Contenido_t.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1449" uniqueCount="593">
   <si>
     <t>.</t>
   </si>
@@ -1309,42 +1309,42 @@
     <t>1.75</t>
   </si>
   <si>
+    <t>360</t>
+  </si>
+  <si>
+    <t>400</t>
+  </si>
+  <si>
+    <t>820</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>540</t>
+  </si>
+  <si>
+    <t>440</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>135</t>
+  </si>
+  <si>
+    <t>432</t>
+  </si>
+  <si>
+    <t>240</t>
+  </si>
+  <si>
     <t>350</t>
   </si>
   <si>
-    <t>400</t>
-  </si>
-  <si>
-    <t>820</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>540</t>
-  </si>
-  <si>
-    <t>440</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>360</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>135</t>
-  </si>
-  <si>
-    <t>432</t>
-  </si>
-  <si>
-    <t>240</t>
-  </si>
-  <si>
     <t>500</t>
   </si>
   <si>
@@ -1514,6 +1514,9 @@
   </si>
   <si>
     <t>La Colonia # 1</t>
+  </si>
+  <si>
+    <t>1.78</t>
   </si>
   <si>
     <t>Pronto</t>
@@ -3893,24 +3896,24 @@
       <c r="R2" s="1"/>
       <c r="S2" s="1"/>
       <c r="T2" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="U2" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="V2" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="V2" s="1" t="s">
+      <c r="W2" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="X2" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="Y2" s="1"/>
       <c r="Z2" s="1"/>
       <c r="AA2" s="1" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="AB2" s="1" t="s">
         <v>443</v>
@@ -3953,53 +3956,53 @@
         <v>449</v>
       </c>
       <c r="AP2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AR2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AS2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AT2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AU2" s="1"/>
       <c r="AV2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AW2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AX2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AY2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AZ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BA2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BB2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BC2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BD2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BE2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BF2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BG2" s="1" t="s">
         <v>450</v>
@@ -4008,7 +4011,7 @@
         <v>451</v>
       </c>
       <c r="BI2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BJ2" s="1"/>
       <c r="BK2" s="1" t="s">
@@ -4024,10 +4027,10 @@
         <v>454</v>
       </c>
       <c r="BO2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BP2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BQ2" s="1"/>
       <c r="BR2" s="1"/>
@@ -4040,7 +4043,7 @@
         <v>456</v>
       </c>
       <c r="BW2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BX2" s="1" t="s">
         <v>444</v>
@@ -4116,92 +4119,92 @@
         <v>432</v>
       </c>
       <c r="DA2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DB2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DC2" s="1"/>
       <c r="DD2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DE2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DF2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DG2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DH2" s="1"/>
       <c r="DI2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DJ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DK2" s="1"/>
       <c r="DL2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DM2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DN2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DO2" s="1" t="s">
         <v>466</v>
       </c>
       <c r="DP2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DQ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DR2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DS2" s="1"/>
       <c r="DT2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DU2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DV2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DW2" s="1"/>
       <c r="DX2" s="1"/>
       <c r="DY2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DZ2" s="1"/>
       <c r="EA2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EB2" s="1" t="s">
         <v>467</v>
       </c>
       <c r="EC2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ED2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EE2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EF2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EG2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EH2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EI2" s="1"/>
       <c r="EJ2" s="1" t="s">
@@ -4229,7 +4232,7 @@
         <v>474</v>
       </c>
       <c r="ET2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EU2" s="1"/>
       <c r="EV2" s="1" t="s">
@@ -4239,7 +4242,7 @@
         <v>476</v>
       </c>
       <c r="EX2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EY2" s="1" t="s">
         <v>477</v>
@@ -4278,7 +4281,7 @@
         <v>450</v>
       </c>
       <c r="FK2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="FL2" s="1" t="s">
         <v>483</v>
@@ -4466,14 +4469,14 @@
       <c r="KS2" s="1"/>
       <c r="KT2" s="1"/>
       <c r="KU2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KV2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KW2" s="1"/>
       <c r="KX2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KY2" s="1"/>
       <c r="KZ2" s="1" t="s">
@@ -4482,10 +4485,10 @@
       <c r="LA2" s="1"/>
       <c r="LB2" s="1"/>
       <c r="LC2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LD2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LE2" s="1"/>
       <c r="LF2" s="1"/>
@@ -4499,13 +4502,13 @@
       <c r="LN2" s="1"/>
       <c r="LO2" s="1"/>
       <c r="LP2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LQ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LR2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LS2" s="1" t="s">
         <v>494</v>
@@ -4517,20 +4520,20 @@
         <v>495</v>
       </c>
       <c r="LV2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LW2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LX2" s="1" t="s">
         <v>482</v>
       </c>
       <c r="LY2" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="LZ2" s="1"/>
       <c r="MA2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MB2" s="1"/>
       <c r="MC2" s="1" t="s">
@@ -4549,19 +4552,19 @@
         <v>466</v>
       </c>
       <c r="MH2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MI2" s="1" t="s">
         <v>498</v>
       </c>
       <c r="MJ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MK2" s="1" t="s">
         <v>434</v>
       </c>
       <c r="ML2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MM2" s="1" t="s">
         <v>432</v>
@@ -4570,13 +4573,13 @@
         <v>437</v>
       </c>
       <c r="MO2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MP2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MQ2" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MR2" s="1"/>
       <c r="MS2" s="1"/>
@@ -4662,11 +4665,11 @@
         <v>429</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>430</v>
+        <v>500</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
@@ -4696,24 +4699,24 @@
       <c r="R3" s="1"/>
       <c r="S3" s="1"/>
       <c r="T3" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="U3" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="V3" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="V3" s="1" t="s">
+      <c r="W3" s="1" t="s">
         <v>440</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>441</v>
-      </c>
-      <c r="X3" s="1" t="s">
-        <v>442</v>
       </c>
       <c r="Y3" s="1"/>
       <c r="Z3" s="1"/>
       <c r="AA3" s="1" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="AB3" s="1" t="s">
         <v>443</v>
@@ -4756,53 +4759,53 @@
         <v>449</v>
       </c>
       <c r="AP3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AQ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AR3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AS3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AT3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AU3" s="1"/>
       <c r="AV3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AW3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AX3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AY3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AZ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BA3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BB3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BC3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BD3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BE3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BF3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BG3" s="1" t="s">
         <v>450</v>
@@ -4811,7 +4814,7 @@
         <v>451</v>
       </c>
       <c r="BI3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BJ3" s="1"/>
       <c r="BK3" s="1" t="s">
@@ -4827,10 +4830,10 @@
         <v>454</v>
       </c>
       <c r="BO3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BP3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BQ3" s="1"/>
       <c r="BR3" s="1"/>
@@ -4843,7 +4846,7 @@
         <v>456</v>
       </c>
       <c r="BW3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BX3" s="1" t="s">
         <v>444</v>
@@ -4919,92 +4922,92 @@
         <v>432</v>
       </c>
       <c r="DA3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DB3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DC3" s="1"/>
       <c r="DD3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DE3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DF3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DG3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DH3" s="1"/>
       <c r="DI3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DJ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DK3" s="1"/>
       <c r="DL3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DM3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DN3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DO3" s="1" t="s">
         <v>466</v>
       </c>
       <c r="DP3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DQ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DR3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DS3" s="1"/>
       <c r="DT3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DU3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DV3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DW3" s="1"/>
       <c r="DX3" s="1"/>
       <c r="DY3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DZ3" s="1"/>
       <c r="EA3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EB3" s="1" t="s">
         <v>467</v>
       </c>
       <c r="EC3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ED3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EE3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EF3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EG3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EH3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EI3" s="1"/>
       <c r="EJ3" s="1" t="s">
@@ -5032,7 +5035,7 @@
         <v>474</v>
       </c>
       <c r="ET3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EU3" s="1"/>
       <c r="EV3" s="1" t="s">
@@ -5042,7 +5045,7 @@
         <v>476</v>
       </c>
       <c r="EX3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EY3" s="1" t="s">
         <v>477</v>
@@ -5081,7 +5084,7 @@
         <v>450</v>
       </c>
       <c r="FK3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="FL3" s="1" t="s">
         <v>483</v>
@@ -5269,14 +5272,14 @@
       <c r="KS3" s="1"/>
       <c r="KT3" s="1"/>
       <c r="KU3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KV3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KW3" s="1"/>
       <c r="KX3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KY3" s="1"/>
       <c r="KZ3" s="1" t="s">
@@ -5285,10 +5288,10 @@
       <c r="LA3" s="1"/>
       <c r="LB3" s="1"/>
       <c r="LC3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LD3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LE3" s="1"/>
       <c r="LF3" s="1"/>
@@ -5302,13 +5305,13 @@
       <c r="LN3" s="1"/>
       <c r="LO3" s="1"/>
       <c r="LP3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LQ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LR3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LS3" s="1" t="s">
         <v>494</v>
@@ -5320,20 +5323,20 @@
         <v>495</v>
       </c>
       <c r="LV3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LW3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LX3" s="1" t="s">
         <v>482</v>
       </c>
       <c r="LY3" s="1" t="s">
-        <v>438</v>
+        <v>431</v>
       </c>
       <c r="LZ3" s="1"/>
       <c r="MA3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MB3" s="1"/>
       <c r="MC3" s="1" t="s">
@@ -5352,19 +5355,19 @@
         <v>466</v>
       </c>
       <c r="MH3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MI3" s="1" t="s">
         <v>498</v>
       </c>
       <c r="MJ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MK3" s="1" t="s">
         <v>434</v>
       </c>
       <c r="ML3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MM3" s="1" t="s">
         <v>432</v>
@@ -5373,13 +5376,13 @@
         <v>437</v>
       </c>
       <c r="MO3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MP3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MQ3" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MR3" s="1"/>
       <c r="MS3" s="1"/>
@@ -5456,13 +5459,13 @@
     </row>
     <row r="4" spans="1:427">
       <c r="A4" s="1" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -5604,7 +5607,7 @@
       <c r="EK4" s="1"/>
       <c r="EL4" s="1"/>
       <c r="EM4" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN4" s="1"/>
       <c r="EO4" s="1"/>
@@ -5893,13 +5896,13 @@
     </row>
     <row r="5" spans="1:427">
       <c r="A5" s="1" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -6041,7 +6044,7 @@
       <c r="EK5" s="1"/>
       <c r="EL5" s="1"/>
       <c r="EM5" s="1" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="EN5" s="1"/>
       <c r="EO5" s="1"/>
@@ -6330,17 +6333,17 @@
     </row>
     <row r="6" spans="1:427">
       <c r="A6" s="1" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F6" s="1"/>
       <c r="G6" s="1"/>
@@ -6374,7 +6377,7 @@
       <c r="AG6" s="1"/>
       <c r="AH6" s="1"/>
       <c r="AI6" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ6" s="1"/>
       <c r="AK6" s="1"/>
@@ -6403,7 +6406,7 @@
       <c r="BH6" s="1"/>
       <c r="BI6" s="1"/>
       <c r="BJ6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BK6" s="1"/>
       <c r="BL6" s="1"/>
@@ -6440,16 +6443,16 @@
       <c r="CM6" s="1"/>
       <c r="CN6" s="1"/>
       <c r="CO6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CP6" s="1"/>
       <c r="CQ6" s="1"/>
       <c r="CR6" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS6" s="1"/>
       <c r="CT6" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU6" s="1"/>
       <c r="CV6" s="1"/>
@@ -6492,7 +6495,7 @@
       <c r="EG6" s="1"/>
       <c r="EH6" s="1"/>
       <c r="EI6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EJ6" s="1"/>
       <c r="EK6" s="1"/>
@@ -6510,7 +6513,7 @@
       <c r="ES6" s="1"/>
       <c r="ET6" s="1"/>
       <c r="EU6" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV6" s="1"/>
       <c r="EW6" s="1"/>
@@ -6534,7 +6537,7 @@
       <c r="FO6" s="1"/>
       <c r="FP6" s="1"/>
       <c r="FQ6" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR6" s="1"/>
       <c r="FS6" s="1"/>
@@ -6703,7 +6706,7 @@
       <c r="LZ6" s="1"/>
       <c r="MA6" s="1"/>
       <c r="MB6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MC6" s="1"/>
       <c r="MD6" s="1"/>
@@ -6795,17 +6798,17 @@
     </row>
     <row r="7" spans="1:427">
       <c r="A7" s="1" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
@@ -6839,7 +6842,7 @@
       <c r="AG7" s="1"/>
       <c r="AH7" s="1"/>
       <c r="AI7" s="1" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="AJ7" s="1"/>
       <c r="AK7" s="1"/>
@@ -6868,7 +6871,7 @@
       <c r="BH7" s="1"/>
       <c r="BI7" s="1"/>
       <c r="BJ7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BK7" s="1"/>
       <c r="BL7" s="1"/>
@@ -6905,16 +6908,16 @@
       <c r="CM7" s="1"/>
       <c r="CN7" s="1"/>
       <c r="CO7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CP7" s="1"/>
       <c r="CQ7" s="1"/>
       <c r="CR7" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="CS7" s="1"/>
       <c r="CT7" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="CU7" s="1"/>
       <c r="CV7" s="1"/>
@@ -6957,7 +6960,7 @@
       <c r="EG7" s="1"/>
       <c r="EH7" s="1"/>
       <c r="EI7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EJ7" s="1"/>
       <c r="EK7" s="1"/>
@@ -6975,7 +6978,7 @@
       <c r="ES7" s="1"/>
       <c r="ET7" s="1"/>
       <c r="EU7" s="1" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="EV7" s="1"/>
       <c r="EW7" s="1"/>
@@ -6999,7 +7002,7 @@
       <c r="FO7" s="1"/>
       <c r="FP7" s="1"/>
       <c r="FQ7" s="1" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="FR7" s="1"/>
       <c r="FS7" s="1"/>
@@ -7168,7 +7171,7 @@
       <c r="LZ7" s="1"/>
       <c r="MA7" s="1"/>
       <c r="MB7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MC7" s="1"/>
       <c r="MD7" s="1"/>
@@ -7260,13 +7263,13 @@
     </row>
     <row r="8" spans="1:427">
       <c r="A8" s="1" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -7519,7 +7522,7 @@
       <c r="IR8" s="1"/>
       <c r="IS8" s="1"/>
       <c r="IT8" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IU8" s="1"/>
       <c r="IV8" s="1"/>
@@ -7697,13 +7700,13 @@
     </row>
     <row r="9" spans="1:427">
       <c r="A9" s="1" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -7956,7 +7959,7 @@
       <c r="IR9" s="1"/>
       <c r="IS9" s="1"/>
       <c r="IT9" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IU9" s="1"/>
       <c r="IV9" s="1"/>
@@ -8134,13 +8137,13 @@
     </row>
     <row r="10" spans="1:427">
       <c r="A10" s="1" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -8394,66 +8397,66 @@
       <c r="IS10" s="1"/>
       <c r="IT10" s="1"/>
       <c r="IU10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IV10" s="1"/>
       <c r="IW10" s="1"/>
       <c r="IX10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IY10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IZ10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JA10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JB10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JC10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JD10" s="1"/>
       <c r="JE10" s="1"/>
       <c r="JF10" s="1"/>
       <c r="JG10" s="1"/>
       <c r="JH10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JI10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JJ10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JK10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JL10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JM10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JN10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JO10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JP10" s="1"/>
       <c r="JQ10" s="1"/>
       <c r="JR10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JS10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JT10" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JU10" s="1"/>
       <c r="JV10" s="1"/>
@@ -8605,13 +8608,13 @@
     </row>
     <row r="11" spans="1:427">
       <c r="A11" s="1" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -8865,66 +8868,66 @@
       <c r="IS11" s="1"/>
       <c r="IT11" s="1"/>
       <c r="IU11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IV11" s="1"/>
       <c r="IW11" s="1"/>
       <c r="IX11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IY11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IZ11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JA11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JB11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JC11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JD11" s="1"/>
       <c r="JE11" s="1"/>
       <c r="JF11" s="1"/>
       <c r="JG11" s="1"/>
       <c r="JH11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JI11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JJ11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JK11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JL11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JM11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JN11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JO11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JP11" s="1"/>
       <c r="JQ11" s="1"/>
       <c r="JR11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JS11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JT11" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JU11" s="1"/>
       <c r="JV11" s="1"/>
@@ -9076,13 +9079,13 @@
     </row>
     <row r="12" spans="1:427">
       <c r="A12" s="1" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -9357,7 +9360,7 @@
       <c r="JN12" s="1"/>
       <c r="JO12" s="1"/>
       <c r="JP12" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JQ12" s="1"/>
       <c r="JR12" s="1"/>
@@ -9513,13 +9516,13 @@
     </row>
     <row r="13" spans="1:427">
       <c r="A13" s="1" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -9794,7 +9797,7 @@
       <c r="JN13" s="1"/>
       <c r="JO13" s="1"/>
       <c r="JP13" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JQ13" s="1"/>
       <c r="JR13" s="1"/>
@@ -9950,13 +9953,13 @@
     </row>
     <row r="14" spans="1:427">
       <c r="A14" s="1" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -10255,26 +10258,26 @@
       <c r="KJ14" s="1"/>
       <c r="KK14" s="1"/>
       <c r="KL14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KM14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KN14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KO14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KP14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KQ14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KR14" s="1"/>
       <c r="KS14" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KT14" s="1"/>
       <c r="KU14" s="1"/>
@@ -10401,13 +10404,13 @@
     </row>
     <row r="15" spans="1:427">
       <c r="A15" s="1" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -10706,26 +10709,26 @@
       <c r="KJ15" s="1"/>
       <c r="KK15" s="1"/>
       <c r="KL15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KM15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KN15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KO15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KP15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KQ15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KR15" s="1"/>
       <c r="KS15" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KT15" s="1"/>
       <c r="KU15" s="1"/>
@@ -10852,13 +10855,13 @@
     </row>
     <row r="16" spans="1:427">
       <c r="A16" s="1" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -11153,7 +11156,7 @@
       <c r="KH16" s="1"/>
       <c r="KI16" s="1"/>
       <c r="KJ16" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KK16" s="1"/>
       <c r="KL16" s="1"/>
@@ -11176,13 +11179,13 @@
       <c r="LC16" s="1"/>
       <c r="LD16" s="1"/>
       <c r="LE16" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LF16" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LG16" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LH16" s="1"/>
       <c r="LI16" s="1"/>
@@ -11295,13 +11298,13 @@
     </row>
     <row r="17" spans="1:427">
       <c r="A17" s="1" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -11596,7 +11599,7 @@
       <c r="KH17" s="1"/>
       <c r="KI17" s="1"/>
       <c r="KJ17" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KK17" s="1"/>
       <c r="KL17" s="1"/>
@@ -11619,13 +11622,13 @@
       <c r="LC17" s="1"/>
       <c r="LD17" s="1"/>
       <c r="LE17" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LF17" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LG17" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LH17" s="1"/>
       <c r="LI17" s="1"/>
@@ -11738,13 +11741,13 @@
     </row>
     <row r="18" spans="1:427">
       <c r="A18" s="1" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -12047,14 +12050,14 @@
       <c r="KP18" s="1"/>
       <c r="KQ18" s="1"/>
       <c r="KR18" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KS18" s="1"/>
       <c r="KT18" s="1"/>
       <c r="KU18" s="1"/>
       <c r="KV18" s="1"/>
       <c r="KW18" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KX18" s="1"/>
       <c r="KY18" s="1" t="s">
@@ -12179,13 +12182,13 @@
     </row>
     <row r="19" spans="1:427">
       <c r="A19" s="1" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -12488,14 +12491,14 @@
       <c r="KP19" s="1"/>
       <c r="KQ19" s="1"/>
       <c r="KR19" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KS19" s="1"/>
       <c r="KT19" s="1"/>
       <c r="KU19" s="1"/>
       <c r="KV19" s="1"/>
       <c r="KW19" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KX19" s="1"/>
       <c r="KY19" s="1" t="s">
@@ -12620,13 +12623,13 @@
     </row>
     <row r="20" spans="1:427">
       <c r="A20" s="1" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -12945,28 +12948,28 @@
       <c r="LF20" s="1"/>
       <c r="LG20" s="1"/>
       <c r="LH20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LI20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LJ20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LK20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LL20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LM20" s="1" t="s">
         <v>479</v>
       </c>
       <c r="LN20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LO20" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LP20" s="1"/>
       <c r="LQ20" s="1"/>
@@ -13071,13 +13074,13 @@
     </row>
     <row r="21" spans="1:427">
       <c r="A21" s="1" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -13396,28 +13399,28 @@
       <c r="LF21" s="1"/>
       <c r="LG21" s="1"/>
       <c r="LH21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LI21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LJ21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LK21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LL21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LM21" s="1" t="s">
         <v>479</v>
       </c>
       <c r="LN21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LO21" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LP21" s="1"/>
       <c r="LQ21" s="1"/>
@@ -13522,13 +13525,13 @@
     </row>
     <row r="22" spans="1:427">
       <c r="A22" s="1" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -13865,7 +13868,7 @@
       <c r="LX22" s="1"/>
       <c r="LY22" s="1"/>
       <c r="LZ22" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA22" s="1"/>
       <c r="MB22" s="1"/>
@@ -13959,13 +13962,13 @@
     </row>
     <row r="23" spans="1:427">
       <c r="A23" s="1" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -14302,7 +14305,7 @@
       <c r="LX23" s="1"/>
       <c r="LY23" s="1"/>
       <c r="LZ23" s="1" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="MA23" s="1"/>
       <c r="MB23" s="1"/>
@@ -14396,13 +14399,13 @@
     </row>
     <row r="24" spans="1:427">
       <c r="A24" s="1" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -14757,49 +14760,49 @@
       <c r="MP24" s="1"/>
       <c r="MQ24" s="1"/>
       <c r="MR24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MS24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MT24" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MV24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MW24" s="1" t="s">
         <v>437</v>
       </c>
       <c r="MX24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY24" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ24" s="1" t="s">
         <v>451</v>
       </c>
       <c r="NA24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NB24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NC24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ND24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NE24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG24" s="1" t="s">
         <v>490</v>
@@ -14820,25 +14823,25 @@
         <v>437</v>
       </c>
       <c r="NM24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NN24" s="1" t="s">
         <v>490</v>
       </c>
       <c r="NO24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NP24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NQ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NS24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NT24" s="1" t="s">
         <v>483</v>
@@ -14847,31 +14850,31 @@
         <v>444</v>
       </c>
       <c r="NV24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NW24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NZ24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OB24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OC24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD24" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE24" s="1" t="s">
         <v>467</v>
@@ -14880,19 +14883,19 @@
         <v>495</v>
       </c>
       <c r="OG24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OH24" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI24" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="OJ24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OK24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OL24" s="1" t="s">
         <v>483</v>
@@ -14901,16 +14904,16 @@
         <v>480</v>
       </c>
       <c r="ON24" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO24" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP24" s="1" t="s">
         <v>437</v>
       </c>
       <c r="OQ24" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OR24" s="1"/>
       <c r="OS24" s="1"/>
@@ -14935,13 +14938,13 @@
     </row>
     <row r="25" spans="1:427">
       <c r="A25" s="1" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -15296,49 +15299,49 @@
       <c r="MP25" s="1"/>
       <c r="MQ25" s="1"/>
       <c r="MR25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MS25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MT25" s="1" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="MU25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MV25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="MW25" s="1" t="s">
         <v>437</v>
       </c>
       <c r="MX25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="MY25" s="1" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="MZ25" s="1" t="s">
         <v>451</v>
       </c>
       <c r="NA25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NB25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NC25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ND25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NE25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NF25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="NG25" s="1" t="s">
         <v>490</v>
@@ -15359,25 +15362,25 @@
         <v>437</v>
       </c>
       <c r="NM25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NN25" s="1" t="s">
         <v>490</v>
       </c>
       <c r="NO25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NP25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NQ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NR25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NS25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NT25" s="1" t="s">
         <v>483</v>
@@ -15386,31 +15389,31 @@
         <v>444</v>
       </c>
       <c r="NV25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NW25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NX25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="NY25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="NZ25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OA25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OB25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OC25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OD25" s="1" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="OE25" s="1" t="s">
         <v>467</v>
@@ -15419,19 +15422,19 @@
         <v>495</v>
       </c>
       <c r="OG25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OH25" s="1" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="OI25" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="OJ25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OK25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OL25" s="1" t="s">
         <v>483</v>
@@ -15440,16 +15443,16 @@
         <v>480</v>
       </c>
       <c r="ON25" s="1" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="OO25" s="1" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="OP25" s="1" t="s">
         <v>437</v>
       </c>
       <c r="OQ25" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OR25" s="1"/>
       <c r="OS25" s="1"/>
@@ -15474,13 +15477,13 @@
     </row>
     <row r="26" spans="1:427">
       <c r="A26" s="1" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -15887,10 +15890,10 @@
       <c r="OP26" s="1"/>
       <c r="OQ26" s="1"/>
       <c r="OR26" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OS26" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OT26" s="1"/>
       <c r="OU26" s="1"/>
@@ -15910,18 +15913,18 @@
       <c r="PI26" s="1"/>
       <c r="PJ26" s="1"/>
       <c r="PK26" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="27" spans="1:427">
       <c r="A27" s="1" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -16328,10 +16331,10 @@
       <c r="OP27" s="1"/>
       <c r="OQ27" s="1"/>
       <c r="OR27" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OS27" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OT27" s="1"/>
       <c r="OU27" s="1"/>
@@ -16351,18 +16354,18 @@
       <c r="PI27" s="1"/>
       <c r="PJ27" s="1"/>
       <c r="PK27" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="28" spans="1:427">
       <c r="A28" s="1" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -16771,41 +16774,41 @@
       <c r="OR28" s="1"/>
       <c r="OS28" s="1"/>
       <c r="OT28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OU28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OV28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OW28" s="1"/>
       <c r="OX28" s="1"/>
       <c r="OY28" s="1"/>
       <c r="OZ28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PA28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PB28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PC28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PD28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PE28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PF28" s="1"/>
       <c r="PG28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PH28" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PI28" s="1"/>
       <c r="PJ28" s="1"/>
@@ -16813,13 +16816,13 @@
     </row>
     <row r="29" spans="1:427">
       <c r="A29" s="1" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B29" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -17228,41 +17231,41 @@
       <c r="OR29" s="1"/>
       <c r="OS29" s="1"/>
       <c r="OT29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OU29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OV29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OW29" s="1"/>
       <c r="OX29" s="1"/>
       <c r="OY29" s="1"/>
       <c r="OZ29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PA29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PB29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PC29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PD29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PE29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PF29" s="1"/>
       <c r="PG29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PH29" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PI29" s="1"/>
       <c r="PJ29" s="1"/>
@@ -17270,13 +17273,13 @@
     </row>
     <row r="30" spans="1:427">
       <c r="A30" s="1" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -17688,13 +17691,13 @@
       <c r="OU30" s="1"/>
       <c r="OV30" s="1"/>
       <c r="OW30" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OX30" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OY30" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OZ30" s="1"/>
       <c r="PA30" s="1"/>
@@ -17711,13 +17714,13 @@
     </row>
     <row r="31" spans="1:427">
       <c r="A31" s="1" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -18129,13 +18132,13 @@
       <c r="OU31" s="1"/>
       <c r="OV31" s="1"/>
       <c r="OW31" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OX31" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OY31" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="OZ31" s="1"/>
       <c r="PA31" s="1"/>
@@ -18152,13 +18155,13 @@
     </row>
     <row r="32" spans="1:427">
       <c r="A32" s="1" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -18579,7 +18582,7 @@
       <c r="PD32" s="1"/>
       <c r="PE32" s="1"/>
       <c r="PF32" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PG32" s="1"/>
       <c r="PH32" s="1"/>
@@ -18589,13 +18592,13 @@
     </row>
     <row r="33" spans="1:427">
       <c r="A33" s="1" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -19016,7 +19019,7 @@
       <c r="PD33" s="1"/>
       <c r="PE33" s="1"/>
       <c r="PF33" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PG33" s="1"/>
       <c r="PH33" s="1"/>
@@ -19026,13 +19029,13 @@
     </row>
     <row r="34" spans="1:427">
       <c r="A34" s="1" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -19456,22 +19459,22 @@
       <c r="PG34" s="1"/>
       <c r="PH34" s="1"/>
       <c r="PI34" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PJ34" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PK34" s="1"/>
     </row>
     <row r="35" spans="1:427">
       <c r="A35" s="1" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -19895,22 +19898,22 @@
       <c r="PG35" s="1"/>
       <c r="PH35" s="1"/>
       <c r="PI35" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PJ35" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="PK35" s="1"/>
     </row>
     <row r="36" spans="1:427">
       <c r="A36" s="1" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -20161,14 +20164,14 @@
       <c r="IP36" s="1"/>
       <c r="IQ36" s="1"/>
       <c r="IR36" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IS36" s="1"/>
       <c r="IT36" s="1"/>
       <c r="IU36" s="1"/>
       <c r="IV36" s="1"/>
       <c r="IW36" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IX36" s="1"/>
       <c r="IY36" s="1"/>
@@ -20343,13 +20346,13 @@
     </row>
     <row r="37" spans="1:427">
       <c r="A37" s="1" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -20600,14 +20603,14 @@
       <c r="IP37" s="1"/>
       <c r="IQ37" s="1"/>
       <c r="IR37" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IS37" s="1"/>
       <c r="IT37" s="1"/>
       <c r="IU37" s="1"/>
       <c r="IV37" s="1"/>
       <c r="IW37" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IX37" s="1"/>
       <c r="IY37" s="1"/>
@@ -20782,13 +20785,13 @@
     </row>
     <row r="38" spans="1:427">
       <c r="A38" s="1" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -20981,16 +20984,16 @@
       <c r="GJ38" s="1"/>
       <c r="GK38" s="1"/>
       <c r="GL38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GM38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GN38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GO38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GP38" s="1"/>
       <c r="GQ38" s="1"/>
@@ -21003,17 +21006,17 @@
       <c r="GT38" s="1"/>
       <c r="GU38" s="1"/>
       <c r="GV38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GW38" s="1"/>
       <c r="GX38" s="1"/>
       <c r="GY38" s="1"/>
       <c r="GZ38" s="1"/>
       <c r="HA38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HB38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HC38" s="1"/>
       <c r="HD38" s="1"/>
@@ -21032,10 +21035,10 @@
       <c r="HQ38" s="1"/>
       <c r="HR38" s="1"/>
       <c r="HS38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HT38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HU38" s="1"/>
       <c r="HV38" s="1"/>
@@ -21056,22 +21059,22 @@
       <c r="IK38" s="1"/>
       <c r="IL38" s="1"/>
       <c r="IM38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IN38" s="1"/>
       <c r="IO38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IP38" s="1"/>
       <c r="IQ38" s="1"/>
       <c r="IR38" s="1"/>
       <c r="IS38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IT38" s="1"/>
       <c r="IU38" s="1"/>
       <c r="IV38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IW38" s="1"/>
       <c r="IX38" s="1"/>
@@ -21081,16 +21084,16 @@
       <c r="JB38" s="1"/>
       <c r="JC38" s="1"/>
       <c r="JD38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JE38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JF38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JG38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JH38" s="1"/>
       <c r="JI38" s="1"/>
@@ -21102,7 +21105,7 @@
       <c r="JO38" s="1"/>
       <c r="JP38" s="1"/>
       <c r="JQ38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JR38" s="1"/>
       <c r="JS38" s="1"/>
@@ -21112,47 +21115,47 @@
         <v>493</v>
       </c>
       <c r="JW38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JX38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JY38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JZ38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KA38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KB38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KC38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KD38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KE38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KF38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KG38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KH38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KI38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KJ38" s="1"/>
       <c r="KK38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KL38" s="1"/>
       <c r="KM38" s="1"/>
@@ -21163,7 +21166,7 @@
       <c r="KR38" s="1"/>
       <c r="KS38" s="1"/>
       <c r="KT38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KU38" s="1"/>
       <c r="KV38" s="1"/>
@@ -21172,10 +21175,10 @@
       <c r="KY38" s="1"/>
       <c r="KZ38" s="1"/>
       <c r="LA38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LB38" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LC38" s="1"/>
       <c r="LD38" s="1"/>
@@ -21293,13 +21296,13 @@
     </row>
     <row r="39" spans="1:427">
       <c r="A39" s="1" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -21492,16 +21495,16 @@
       <c r="GJ39" s="1"/>
       <c r="GK39" s="1"/>
       <c r="GL39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GM39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GN39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GO39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GP39" s="1"/>
       <c r="GQ39" s="1"/>
@@ -21514,17 +21517,17 @@
       <c r="GT39" s="1"/>
       <c r="GU39" s="1"/>
       <c r="GV39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GW39" s="1"/>
       <c r="GX39" s="1"/>
       <c r="GY39" s="1"/>
       <c r="GZ39" s="1"/>
       <c r="HA39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HB39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HC39" s="1"/>
       <c r="HD39" s="1"/>
@@ -21543,10 +21546,10 @@
       <c r="HQ39" s="1"/>
       <c r="HR39" s="1"/>
       <c r="HS39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HT39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HU39" s="1"/>
       <c r="HV39" s="1"/>
@@ -21567,22 +21570,22 @@
       <c r="IK39" s="1"/>
       <c r="IL39" s="1"/>
       <c r="IM39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IN39" s="1"/>
       <c r="IO39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IP39" s="1"/>
       <c r="IQ39" s="1"/>
       <c r="IR39" s="1"/>
       <c r="IS39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IT39" s="1"/>
       <c r="IU39" s="1"/>
       <c r="IV39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IW39" s="1"/>
       <c r="IX39" s="1"/>
@@ -21592,16 +21595,16 @@
       <c r="JB39" s="1"/>
       <c r="JC39" s="1"/>
       <c r="JD39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JE39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JF39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JG39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JH39" s="1"/>
       <c r="JI39" s="1"/>
@@ -21613,7 +21616,7 @@
       <c r="JO39" s="1"/>
       <c r="JP39" s="1"/>
       <c r="JQ39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JR39" s="1"/>
       <c r="JS39" s="1"/>
@@ -21623,47 +21626,47 @@
         <v>493</v>
       </c>
       <c r="JW39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JX39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JY39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="JZ39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KA39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KB39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KC39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KD39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KE39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KF39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KG39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KH39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KI39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KJ39" s="1"/>
       <c r="KK39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KL39" s="1"/>
       <c r="KM39" s="1"/>
@@ -21674,7 +21677,7 @@
       <c r="KR39" s="1"/>
       <c r="KS39" s="1"/>
       <c r="KT39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="KU39" s="1"/>
       <c r="KV39" s="1"/>
@@ -21683,10 +21686,10 @@
       <c r="KY39" s="1"/>
       <c r="KZ39" s="1"/>
       <c r="LA39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LB39" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="LC39" s="1"/>
       <c r="LD39" s="1"/>
@@ -21804,13 +21807,13 @@
     </row>
     <row r="40" spans="1:427">
       <c r="A40" s="1" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -22001,10 +22004,10 @@
       <c r="GH40" s="1"/>
       <c r="GI40" s="1"/>
       <c r="GJ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GK40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GL40" s="1"/>
       <c r="GM40" s="1"/>
@@ -22019,123 +22022,123 @@
       <c r="GR40" s="1"/>
       <c r="GS40" s="1"/>
       <c r="GT40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GU40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GV40" s="1"/>
       <c r="GW40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GX40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GY40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GZ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HA40" s="1"/>
       <c r="HB40" s="1"/>
       <c r="HC40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HD40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HE40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HF40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HG40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HH40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HI40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HJ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HK40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HL40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HM40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HN40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HO40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HP40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HQ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HR40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HS40" s="1"/>
       <c r="HT40" s="1"/>
       <c r="HU40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HV40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HW40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HX40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HY40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HZ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IA40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IB40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IC40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ID40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IE40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IF40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IG40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IH40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="II40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IJ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IK40" s="1" t="s">
         <v>493</v>
@@ -22145,14 +22148,14 @@
       </c>
       <c r="IM40" s="1"/>
       <c r="IN40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IO40" s="1"/>
       <c r="IP40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IQ40" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IR40" s="1"/>
       <c r="IS40" s="1"/>
@@ -22333,13 +22336,13 @@
     </row>
     <row r="41" spans="1:427">
       <c r="A41" s="1" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -22530,10 +22533,10 @@
       <c r="GH41" s="1"/>
       <c r="GI41" s="1"/>
       <c r="GJ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GK41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GL41" s="1"/>
       <c r="GM41" s="1"/>
@@ -22548,123 +22551,123 @@
       <c r="GR41" s="1"/>
       <c r="GS41" s="1"/>
       <c r="GT41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GU41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GV41" s="1"/>
       <c r="GW41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GX41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GY41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="GZ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HA41" s="1"/>
       <c r="HB41" s="1"/>
       <c r="HC41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HD41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HE41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HF41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HG41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HH41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HI41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HJ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HK41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HL41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HM41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HN41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HO41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HP41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HQ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HR41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HS41" s="1"/>
       <c r="HT41" s="1"/>
       <c r="HU41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HV41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HW41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HX41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HY41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="HZ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IA41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IB41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IC41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="ID41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IE41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IF41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IG41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IH41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="II41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IJ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IK41" s="1" t="s">
         <v>493</v>
@@ -22674,14 +22677,14 @@
       </c>
       <c r="IM41" s="1"/>
       <c r="IN41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IO41" s="1"/>
       <c r="IP41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IQ41" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="IR41" s="1"/>
       <c r="IS41" s="1"/>
@@ -22862,13 +22865,13 @@
     </row>
     <row r="42" spans="1:427">
       <c r="A42" s="1" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -22974,19 +22977,19 @@
       <c r="DA42" s="1"/>
       <c r="DB42" s="1"/>
       <c r="DC42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DD42" s="1"/>
       <c r="DE42" s="1"/>
       <c r="DF42" s="1"/>
       <c r="DG42" s="1"/>
       <c r="DH42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DI42" s="1"/>
       <c r="DJ42" s="1"/>
       <c r="DK42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DL42" s="1"/>
       <c r="DM42" s="1"/>
@@ -22996,20 +22999,20 @@
       <c r="DQ42" s="1"/>
       <c r="DR42" s="1"/>
       <c r="DS42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DT42" s="1"/>
       <c r="DU42" s="1"/>
       <c r="DV42" s="1"/>
       <c r="DW42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DX42" s="1" t="s">
         <v>451</v>
       </c>
       <c r="DY42" s="1"/>
       <c r="DZ42" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EA42" s="1"/>
       <c r="EB42" s="1"/>
@@ -23311,13 +23314,13 @@
     </row>
     <row r="43" spans="1:427">
       <c r="A43" s="1" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -23423,19 +23426,19 @@
       <c r="DA43" s="1"/>
       <c r="DB43" s="1"/>
       <c r="DC43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DD43" s="1"/>
       <c r="DE43" s="1"/>
       <c r="DF43" s="1"/>
       <c r="DG43" s="1"/>
       <c r="DH43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DI43" s="1"/>
       <c r="DJ43" s="1"/>
       <c r="DK43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DL43" s="1"/>
       <c r="DM43" s="1"/>
@@ -23445,20 +23448,20 @@
       <c r="DQ43" s="1"/>
       <c r="DR43" s="1"/>
       <c r="DS43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DT43" s="1"/>
       <c r="DU43" s="1"/>
       <c r="DV43" s="1"/>
       <c r="DW43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="DX43" s="1" t="s">
         <v>451</v>
       </c>
       <c r="DY43" s="1"/>
       <c r="DZ43" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="EA43" s="1"/>
       <c r="EB43" s="1"/>
@@ -23760,13 +23763,13 @@
     </row>
     <row r="44" spans="1:427">
       <c r="A44" s="1" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -23837,7 +23840,7 @@
       <c r="BR44" s="1"/>
       <c r="BS44" s="1"/>
       <c r="BT44" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BU44" s="1"/>
       <c r="BV44" s="1"/>
@@ -24197,13 +24200,13 @@
     </row>
     <row r="45" spans="1:427">
       <c r="A45" s="1" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -24274,7 +24277,7 @@
       <c r="BR45" s="1"/>
       <c r="BS45" s="1"/>
       <c r="BT45" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BU45" s="1"/>
       <c r="BV45" s="1"/>
@@ -24634,13 +24637,13 @@
     </row>
     <row r="46" spans="1:427">
       <c r="A46" s="1" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -24708,13 +24711,13 @@
       <c r="BO46" s="1"/>
       <c r="BP46" s="1"/>
       <c r="BQ46" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BR46" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BS46" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BT46" s="1"/>
       <c r="BU46" s="1"/>
@@ -25075,13 +25078,13 @@
     </row>
     <row r="47" spans="1:427">
       <c r="A47" s="1" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -25149,13 +25152,13 @@
       <c r="BO47" s="1"/>
       <c r="BP47" s="1"/>
       <c r="BQ47" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BR47" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BS47" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="BT47" s="1"/>
       <c r="BU47" s="1"/>
@@ -25516,13 +25519,13 @@
     </row>
     <row r="48" spans="1:427">
       <c r="A48" s="1" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -25568,7 +25571,7 @@
       <c r="AS48" s="1"/>
       <c r="AT48" s="1"/>
       <c r="AU48" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AV48" s="1"/>
       <c r="AW48" s="1"/>
@@ -25953,13 +25956,13 @@
     </row>
     <row r="49" spans="1:427">
       <c r="A49" s="1" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -26005,7 +26008,7 @@
       <c r="AS49" s="1"/>
       <c r="AT49" s="1"/>
       <c r="AU49" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AV49" s="1"/>
       <c r="AW49" s="1"/>
@@ -26390,13 +26393,13 @@
     </row>
     <row r="50" spans="1:427">
       <c r="A50" s="1" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -26414,7 +26417,7 @@
       <c r="Q50" s="1"/>
       <c r="R50" s="1"/>
       <c r="S50" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T50" s="1"/>
       <c r="U50" s="1"/>
@@ -26827,13 +26830,13 @@
     </row>
     <row r="51" spans="1:427">
       <c r="A51" s="1" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -26851,7 +26854,7 @@
       <c r="Q51" s="1"/>
       <c r="R51" s="1"/>
       <c r="S51" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="T51" s="1"/>
       <c r="U51" s="1"/>
@@ -27264,13 +27267,13 @@
     </row>
     <row r="52" spans="1:427">
       <c r="A52" s="1" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -27280,10 +27283,10 @@
       <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L52" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M52" s="1"/>
       <c r="N52" s="1" t="s">
@@ -27300,10 +27303,10 @@
       <c r="W52" s="1"/>
       <c r="X52" s="1"/>
       <c r="Y52" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Z52" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AA52" s="1"/>
       <c r="AB52" s="1"/>
@@ -27709,13 +27712,13 @@
     </row>
     <row r="53" spans="1:427">
       <c r="A53" s="1" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -27725,10 +27728,10 @@
       <c r="I53" s="1"/>
       <c r="J53" s="1"/>
       <c r="K53" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="M53" s="1"/>
       <c r="N53" s="1" t="s">
@@ -27745,10 +27748,10 @@
       <c r="W53" s="1"/>
       <c r="X53" s="1"/>
       <c r="Y53" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Z53" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AA53" s="1"/>
       <c r="AB53" s="1"/>
@@ -28154,19 +28157,19 @@
     </row>
     <row r="54" spans="1:427">
       <c r="A54" s="1" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -28591,19 +28594,19 @@
     </row>
     <row r="55" spans="1:427">
       <c r="A55" s="1" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B55" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C55" s="1" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -29028,13 +29031,13 @@
     </row>
     <row r="56" spans="1:427">
       <c r="A56" s="1" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C56" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -29117,23 +29120,23 @@
       <c r="CD56" s="1"/>
       <c r="CE56" s="1"/>
       <c r="CF56" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CG56" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CH56" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CI56" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CJ56" s="1"/>
       <c r="CK56" s="1"/>
       <c r="CL56" s="1"/>
       <c r="CM56" s="1"/>
       <c r="CN56" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CO56" s="1"/>
       <c r="CP56" s="1"/>
@@ -29473,13 +29476,13 @@
     </row>
     <row r="57" spans="1:427">
       <c r="A57" s="1" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>428</v>
       </c>
       <c r="C57" s="1" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -29562,23 +29565,23 @@
       <c r="CD57" s="1"/>
       <c r="CE57" s="1"/>
       <c r="CF57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CG57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CH57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CI57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CJ57" s="1"/>
       <c r="CK57" s="1"/>
       <c r="CL57" s="1"/>
       <c r="CM57" s="1"/>
       <c r="CN57" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="CO57" s="1"/>
       <c r="CP57" s="1"/>
